--- a/fc/web-app/docs/samples/FC-TakoffLandingCalculation-Sample.xlsx
+++ b/fc/web-app/docs/samples/FC-TakoffLandingCalculation-Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\EPJ\fcdev\fc\web-app\docs\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B900E76-3978-4526-9DC9-0F602DE3F44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF9C348-970A-44CE-8E7E-4CB840A60B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18525" yWindow="3720" windowWidth="18000" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="An-Abflug-Berechnung" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -99,16 +102,16 @@
     <t>An-/Abflugberechnung</t>
   </si>
   <si>
-    <t>Wettbewerb 2017</t>
-  </si>
-  <si>
-    <t>Veranstalter</t>
-  </si>
-  <si>
-    <t>Version 4</t>
-  </si>
-  <si>
     <t>Ausgemessene</t>
+  </si>
+  <si>
+    <t>Version 5</t>
+  </si>
+  <si>
+    <t>Wettbewerb</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
 </sst>
 </file>
@@ -187,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -227,10 +230,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -597,19 +603,17 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="B4" s="5"/>
       <c r="F4" s="2" t="s">
         <v>13</v>
       </c>
@@ -628,15 +632,15 @@
         <v>5</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="15"/>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="7"/>
@@ -674,200 +678,211 @@
       <c r="B11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="6">
-        <v>4.53</v>
+      <c r="C11" s="15">
+        <v>4</v>
       </c>
       <c r="D11" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="15">
         <v>9</v>
       </c>
-      <c r="F11" s="16">
-        <v>9.1</v>
-      </c>
-      <c r="G11" s="2">
+      <c r="G11" s="17">
         <f>F11-C11</f>
-        <v>4.5699999999999994</v>
-      </c>
-      <c r="H11" s="2">
+        <v>5</v>
+      </c>
+      <c r="H11" s="17">
         <f>D11+G11</f>
-        <v>4.5699999999999994</v>
+        <v>8</v>
       </c>
       <c r="I11" s="2" t="str">
         <f>CONCATENATE("wind+:",ROUND(H11,1),"NM")</f>
-        <v>wind+:4,6NM</v>
+        <v>wind+:8NM</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="E12" s="6">
-        <v>24</v>
-      </c>
-      <c r="F12" s="16">
-        <v>8.9</v>
-      </c>
-      <c r="G12" s="2">
+      <c r="E12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="15">
+        <v>8</v>
+      </c>
+      <c r="G12" s="17">
         <f>F12-C11</f>
-        <v>4.37</v>
-      </c>
-      <c r="H12" s="2">
+        <v>4</v>
+      </c>
+      <c r="H12" s="17">
         <f>D11+G12</f>
-        <v>4.37</v>
+        <v>7</v>
       </c>
       <c r="I12" s="2" t="str">
         <f>CONCATENATE("wind+:",ROUND(H12,1),"NM")</f>
-        <v>wind+:4,4NM</v>
-      </c>
+        <v>wind+:7NM</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="6">
-        <v>4.22</v>
+      <c r="C14" s="15">
+        <v>5</v>
       </c>
       <c r="D14" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="16">
-        <v>6.7</v>
-      </c>
-      <c r="G14" s="2">
+        <v>10</v>
+      </c>
+      <c r="F14" s="15">
+        <v>6</v>
+      </c>
+      <c r="G14" s="17">
         <f>F14-C14</f>
-        <v>2.4800000000000004</v>
-      </c>
-      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="17">
         <f>D14+G14</f>
-        <v>2.4800000000000004</v>
+        <v>4</v>
       </c>
       <c r="I14" s="2" t="str">
         <f>CONCATENATE("wind+:",ROUND(H14,1),"NM")</f>
-        <v>wind+:2,5NM</v>
+        <v>wind+:4NM</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="16">
-        <v>6.6</v>
-      </c>
-      <c r="G15" s="2">
+        <v>11</v>
+      </c>
+      <c r="F15" s="15">
+        <v>7</v>
+      </c>
+      <c r="G15" s="17">
         <f>F15-C14</f>
-        <v>2.38</v>
-      </c>
-      <c r="H15" s="2">
+        <v>2</v>
+      </c>
+      <c r="H15" s="17">
         <f>D14+G15</f>
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="I15" s="2" t="str">
         <f>CONCATENATE("wind+:",ROUND(H15,1),"NM")</f>
-        <v>wind+:2,4NM</v>
-      </c>
+        <v>wind+:5NM</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="6">
-        <v>3.99</v>
+      <c r="C17" s="15">
+        <v>4</v>
       </c>
       <c r="D17" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="12" t="str">
         <f>E14</f>
-        <v>09</v>
-      </c>
-      <c r="F17" s="16">
-        <v>7.8</v>
-      </c>
-      <c r="G17" s="2">
+        <v>27</v>
+      </c>
+      <c r="F17" s="15">
+        <v>8</v>
+      </c>
+      <c r="G17" s="17">
         <f>F17-C17</f>
-        <v>3.8099999999999996</v>
-      </c>
-      <c r="H17" s="2">
+        <v>4</v>
+      </c>
+      <c r="H17" s="17">
         <f>D17+G17</f>
-        <v>3.8099999999999996</v>
+        <v>7</v>
       </c>
       <c r="I17" s="2" t="str">
         <f>CONCATENATE("wind+:",ROUND(H17,1),"NM")</f>
-        <v>wind+:3,8NM</v>
+        <v>wind+:7NM</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E18" s="12" t="str">
         <f>E15</f>
-        <v>27</v>
-      </c>
-      <c r="F18" s="16">
+        <v>09</v>
+      </c>
+      <c r="F18" s="15">
+        <v>9</v>
+      </c>
+      <c r="G18" s="17">
+        <f>F18-C17</f>
+        <v>5</v>
+      </c>
+      <c r="H18" s="17">
+        <f>D17+G18</f>
         <v>8</v>
-      </c>
-      <c r="G18" s="2">
-        <f>F18-C17</f>
-        <v>4.01</v>
-      </c>
-      <c r="H18" s="2">
-        <f>D17+G18</f>
-        <v>4.01</v>
       </c>
       <c r="I18" s="2" t="str">
         <f>CONCATENATE("wind+:",ROUND(H18,1),"NM")</f>
-        <v>wind+:4NM</v>
-      </c>
+        <v>wind+:8NM</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="6">
-        <v>3.15</v>
+      <c r="C20" s="15">
+        <v>3</v>
       </c>
       <c r="D20" s="10">
         <v>3</v>
       </c>
       <c r="E20" s="12" t="str">
         <f>E11</f>
-        <v>06</v>
-      </c>
-      <c r="F20" s="16">
-        <v>5.7</v>
-      </c>
-      <c r="G20" s="2">
+        <v>24</v>
+      </c>
+      <c r="F20" s="15">
+        <v>8</v>
+      </c>
+      <c r="G20" s="17">
         <f>F20-C20</f>
-        <v>2.5500000000000003</v>
-      </c>
-      <c r="H20" s="2">
+        <v>5</v>
+      </c>
+      <c r="H20" s="17">
         <f>D20+G20</f>
-        <v>5.5500000000000007</v>
+        <v>8</v>
       </c>
       <c r="I20" s="2" t="str">
         <f>CONCATENATE("wind+:",ROUND(H20,1),"NM")</f>
-        <v>wind+:5,6NM</v>
+        <v>wind+:8NM</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="E21" s="12">
+      <c r="E21" s="12" t="str">
         <f>E12</f>
-        <v>24</v>
-      </c>
-      <c r="F21" s="16">
+        <v>06</v>
+      </c>
+      <c r="F21" s="15">
         <v>9</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="17">
         <f>F21-C20</f>
-        <v>5.85</v>
-      </c>
-      <c r="H21" s="2">
+        <v>6</v>
+      </c>
+      <c r="H21" s="17">
         <f>D20+G21</f>
-        <v>8.85</v>
+        <v>9</v>
       </c>
       <c r="I21" s="2" t="str">
         <f>CONCATENATE("wind+:",ROUND(H21,1),"NM")</f>
-        <v>wind+:8,9NM</v>
+        <v>wind+:9NM</v>
       </c>
     </row>
   </sheetData>
